--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/3024-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/3024-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB74EF3A-8ED6-4612-B05E-8338AA6EC624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{97DF4B6D-D274-498C-98C5-DEDF307C0019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{13082C01-8CA3-4F6B-97EB-96F87D3D1CAA}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{5F46648D-FBBA-4852-A540-D836CEAB5781}"/>
   </bookViews>
   <sheets>
     <sheet name="3024-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1472,27 +1472,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00FA52C4-366C-4D74-A310-C19046C94513}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAFB1F51-F94D-40AB-8B0F-38E18FE71495}">
   <dimension ref="A1:X45"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="6.25" customWidth="1"/>
-    <col min="15" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -1526,7 +1525,7 @@
       <c r="W1" s="27"/>
       <c r="X1" s="19"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -1562,7 +1561,7 @@
       <c r="W2" s="29"/>
       <c r="X2" s="30"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
@@ -1614,7 +1613,7 @@
       </c>
       <c r="X3" s="33"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="22"/>
       <c r="B4" s="23"/>
       <c r="C4" s="7"/>
@@ -1682,7 +1681,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="34">
         <v>2024</v>
       </c>
@@ -1754,7 +1753,7 @@
         <v>4.04</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="36">
         <v>2023</v>
       </c>
@@ -1826,7 +1825,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="34">
         <v>2022</v>
       </c>
@@ -1898,7 +1897,7 @@
         <v>1.69</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="36">
         <v>2021</v>
       </c>
@@ -1970,7 +1969,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="34">
         <v>2020</v>
       </c>
@@ -2042,7 +2041,7 @@
         <v>1.01</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="36">
         <v>2019</v>
       </c>
@@ -2114,7 +2113,7 @@
         <v>3.95</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="34">
         <v>2018</v>
       </c>
@@ -2186,7 +2185,7 @@
         <v>5.41</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="36">
         <v>2017</v>
       </c>
@@ -2258,7 +2257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="34">
         <v>2016</v>
       </c>
@@ -2330,7 +2329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="36">
         <v>2015</v>
       </c>
@@ -2402,7 +2401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="34">
         <v>2014</v>
       </c>
@@ -2474,7 +2473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="36">
         <v>2013</v>
       </c>
@@ -2546,7 +2545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="34">
         <v>2012</v>
       </c>
@@ -2618,7 +2617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="36">
         <v>2011</v>
       </c>
@@ -2690,7 +2689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="34">
         <v>2010</v>
       </c>
@@ -2762,7 +2761,7 @@
         <v>7.96</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="36">
         <v>2009</v>
       </c>
@@ -2834,7 +2833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="34">
         <v>2008</v>
       </c>
@@ -2906,7 +2905,7 @@
         <v>6.41</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="36">
         <v>2007</v>
       </c>
@@ -2978,7 +2977,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="34">
         <v>2006</v>
       </c>
@@ -3050,7 +3049,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="36">
         <v>2005</v>
       </c>
@@ -3122,7 +3121,7 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="34">
         <v>2004</v>
       </c>
@@ -3194,7 +3193,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="36">
         <v>2003</v>
       </c>
@@ -3266,7 +3265,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="34">
         <v>2002</v>
       </c>
@@ -3338,7 +3337,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="36">
         <v>2001</v>
       </c>
@@ -3410,7 +3409,7 @@
         <v>5.05</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="34">
         <v>2000</v>
       </c>
@@ -3482,7 +3481,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="36">
         <v>1999</v>
       </c>
@@ -3554,7 +3553,7 @@
         <v>15.9</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="34">
         <v>1998</v>
       </c>
@@ -3626,7 +3625,7 @@
         <v>7.56</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="36">
         <v>1997</v>
       </c>
@@ -3698,7 +3697,7 @@
         <v>5.81</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="34">
         <v>1996</v>
       </c>
@@ -3770,7 +3769,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="36">
         <v>1995</v>
       </c>
@@ -3842,7 +3841,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="34">
         <v>1994</v>
       </c>
@@ -3914,7 +3913,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="36">
         <v>1993</v>
       </c>
@@ -3986,7 +3985,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="34">
         <v>1992</v>
       </c>
@@ -4058,7 +4057,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="36">
         <v>1991</v>
       </c>
@@ -4130,7 +4129,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="34">
         <v>1989</v>
       </c>
@@ -4202,7 +4201,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="36">
         <v>1987</v>
       </c>
@@ -4274,7 +4273,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="34">
         <v>1985</v>
       </c>
@@ -4346,7 +4345,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="36">
         <v>1983</v>
       </c>
@@ -4418,7 +4417,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="34">
         <v>1981</v>
       </c>
@@ -4490,7 +4489,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="36">
         <v>1978</v>
       </c>
@@ -4562,7 +4561,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="34" t="s">
         <v>49</v>
       </c>
